--- a/data/trans_camb/P29A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 9,98</t>
+          <t>0,79; 10,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 6,74</t>
+          <t>-2,88; 6,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 9,31</t>
+          <t>-1,17; 9,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,87</t>
+          <t>0,55; 5,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,17</t>
+          <t>-1,46; 4,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,38</t>
+          <t>-4,87; -0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,04</t>
+          <t>0,62; 6,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,09</t>
+          <t>-1,36; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,01</t>
+          <t>-3,21; 2,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 24,01</t>
+          <t>1,55; 24,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 16,4</t>
+          <t>-6,34; 16,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 22,39</t>
+          <t>-2,5; 22,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 57,57</t>
+          <t>4,31; 58,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 41,78</t>
+          <t>-10,62; 43,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 3,59</t>
+          <t>-38,11; 0,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 25,52</t>
+          <t>2,22; 24,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 17,03</t>
+          <t>-5,26; 15,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 8,42</t>
+          <t>-12,13; 8,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,49</t>
+          <t>-6,19; 0,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,03</t>
+          <t>-4,86; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,11; -10,75</t>
+          <t>-28,91; -10,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 1,24</t>
+          <t>-5,71; 1,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,6</t>
+          <t>0,04; 6,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 18,71</t>
+          <t>-7,81; 18,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,03</t>
+          <t>-4,76; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,12</t>
+          <t>-1,79; 3,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,46; -0,32</t>
+          <t>-14,61; -0,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 0,82</t>
+          <t>-10,02; 1,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,48</t>
+          <t>-7,89; 3,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,43; -17,96</t>
+          <t>-47,62; -17,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 4,17</t>
+          <t>-17,2; 3,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 22,65</t>
+          <t>0,21; 22,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 63,33</t>
+          <t>-24,22; 59,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 0,17</t>
+          <t>-9,93; 0,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,94</t>
+          <t>-3,72; 6,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -0,8</t>
+          <t>-30,94; -0,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 11,1</t>
+          <t>-1,3; 10,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,65</t>
+          <t>0,64; 12,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -1,37</t>
+          <t>-13,23; -1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 14,46</t>
+          <t>0,63; 13,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 17,42</t>
+          <t>5,18; 17,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 4,62</t>
+          <t>-6,47; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 10,17</t>
+          <t>0,71; 9,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 13,04</t>
+          <t>4,46; 13,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -0,58</t>
+          <t>-9,34; -0,39</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 19,4</t>
+          <t>-2,1; 18,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 23,99</t>
+          <t>0,98; 22,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,9; -1,89</t>
+          <t>-20,81; -2,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 40,19</t>
+          <t>1,63; 37,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 50,06</t>
+          <t>12,31; 51,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 13,25</t>
+          <t>-15,35; 13,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 21,22</t>
+          <t>1,35; 20,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 27,33</t>
+          <t>8,4; 27,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,19; -1,12</t>
+          <t>-17,98; -0,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 3,35</t>
+          <t>-1,29; 3,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,33</t>
+          <t>-0,27; 4,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,44; -4,96</t>
+          <t>-20,5; -4,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,39</t>
+          <t>-1,01; 3,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,54</t>
+          <t>4,08; 8,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 16,17</t>
+          <t>-1,49; 18,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,78</t>
+          <t>-0,7; 2,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,8</t>
+          <t>2,46; 5,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,02</t>
+          <t>-6,66; 2,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 6,29</t>
+          <t>-2,28; 6,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,1</t>
+          <t>-0,49; 8,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,27; -9,1</t>
+          <t>-36,81; -8,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 14,43</t>
+          <t>-4,01; 14,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,5; 36,3</t>
+          <t>16,07; 35,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 63,94</t>
+          <t>-5,98; 73,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,29</t>
+          <t>-1,72; 7,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,96; 14,92</t>
+          <t>6,02; 15,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 7,64</t>
+          <t>-16,67; 7,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P29A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P29A_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-1,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,04</t>
+          <t>1,47; 10,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 6,81</t>
+          <t>-2,64; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 9,55</t>
+          <t>-3,83; 6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,87</t>
+          <t>0,48; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,42</t>
+          <t>-1,28; 4,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -0,0</t>
+          <t>-4,39; 0,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,0</t>
+          <t>0,62; 6,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,8</t>
+          <t>-1,22; 4,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,17</t>
+          <t>-4,08; 1,54</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,57%</t>
+          <t>-18,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-2,9%</t>
+          <t>-5,79%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 24,41</t>
+          <t>3,48; 24,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 16,42</t>
+          <t>-5,8; 16,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 22,97</t>
+          <t>-8,49; 15,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 58,88</t>
+          <t>3,89; 59,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 43,26</t>
+          <t>-10,39; 43,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 0,83</t>
+          <t>-35,22; 3,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 24,45</t>
+          <t>2,18; 25,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 15,69</t>
+          <t>-4,43; 17,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 8,57</t>
+          <t>-15,56; 6,29</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-17,06</t>
+          <t>-13,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,69</t>
+          <t>-9,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,74</t>
+          <t>-6,05; 0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,88</t>
+          <t>-4,77; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,91; -10,48</t>
+          <t>-16,51; -9,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,05</t>
+          <t>-5,48; 0,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,58</t>
+          <t>0,39; 6,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 18,86</t>
+          <t>-8,59; -2,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,23</t>
+          <t>-4,74; 0,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,0</t>
+          <t>-1,64; 3,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,61; -0,53</t>
+          <t>-12,16; -7,36</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,34%</t>
+          <t>-21,8%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>-17,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,8%</t>
+          <t>-20,79%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 1,31</t>
+          <t>-9,8; 1,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,26</t>
+          <t>-7,74; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,62; -17,74</t>
+          <t>-26,67; -16,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 3,68</t>
+          <t>-16,79; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 22,25</t>
+          <t>1,11; 22,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 59,96</t>
+          <t>-25,82; -9,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 0,54</t>
+          <t>-9,97; 0,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 6,67</t>
+          <t>-3,47; 6,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -0,97</t>
+          <t>-25,44; -16,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,24</t>
+          <t>-8,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,9</t>
+          <t>-5,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 10,71</t>
+          <t>-1,71; 11,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 12,86</t>
+          <t>1,05; 13,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,23; -1,41</t>
+          <t>-14,39; -2,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 13,26</t>
+          <t>0,25; 13,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,18; 17,88</t>
+          <t>5,4; 17,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 4,54</t>
+          <t>-7,01; 4,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,29; 10,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 13,24</t>
+          <t>4,44; 13,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,34; -0,39</t>
+          <t>-9,89; -1,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-11,97%</t>
+          <t>-14,48%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,5%</t>
+          <t>-3,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,77%</t>
+          <t>-11,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 18,73</t>
+          <t>-2,63; 20,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 22,29</t>
+          <t>1,74; 23,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -2,12</t>
+          <t>-22,78; -4,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 37,65</t>
+          <t>0,49; 38,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 51,03</t>
+          <t>12,54; 51,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 13,2</t>
+          <t>-16,95; 12,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 20,02</t>
+          <t>0,58; 21,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,4; 27,52</t>
+          <t>8,53; 27,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -0,89</t>
+          <t>-18,92; -3,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,26</t>
+          <t>-7,3</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,72</t>
+          <t>-1,42; 3,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,44</t>
+          <t>-0,25; 4,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -4,53</t>
+          <t>-10,12; -4,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,29</t>
+          <t>-0,86; 3,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,3</t>
+          <t>4,03; 8,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 18,31</t>
+          <t>-2,06; 1,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,81</t>
+          <t>-0,79; 2,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,85</t>
+          <t>2,44; 5,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,99</t>
+          <t>-5,29; -1,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,85%</t>
+          <t>-13,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>-0,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>-9,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 6,96</t>
+          <t>-2,52; 6,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,28</t>
+          <t>-0,58; 8,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,81; -8,54</t>
+          <t>-18,2; -8,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 14,12</t>
+          <t>-3,37; 14,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,07; 35,09</t>
+          <t>15,68; 35,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 73,04</t>
+          <t>-8,09; 8,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,36</t>
+          <t>-1,96; 7,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,03</t>
+          <t>6,08; 15,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 7,97</t>
+          <t>-13,11; -5,04</t>
         </is>
       </c>
     </row>
